--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.004113816047243</v>
+        <v>0.9756684951076771</v>
       </c>
       <c r="D2" t="n">
-        <v>41.3817768537166</v>
+        <v>6.724538738728948</v>
       </c>
       <c r="E2" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F2" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.51507089377866</v>
+        <v>3.983699020239033</v>
       </c>
       <c r="D3" t="n">
-        <v>52.50570460757595</v>
+        <v>8.532176998731092</v>
       </c>
       <c r="E3" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F3" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.48064438606548</v>
+        <v>8.040604712735641</v>
       </c>
       <c r="D4" t="n">
-        <v>30.71388690389167</v>
+        <v>4.991006621882396</v>
       </c>
       <c r="E4" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F4" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.05852770944816</v>
+        <v>6.834510752785327</v>
       </c>
       <c r="D5" t="n">
-        <v>20.89865106884615</v>
+        <v>3.396030798687499</v>
       </c>
       <c r="E5" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F5" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.38055220857147</v>
+        <v>5.586839733892864</v>
       </c>
       <c r="D6" t="n">
-        <v>4.647158849283864</v>
+        <v>0.7551633130086279</v>
       </c>
       <c r="E6" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F6" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.45740301714329</v>
+        <v>7.549327990285784</v>
       </c>
       <c r="D7" t="n">
-        <v>25.92595310291709</v>
+        <v>4.212967379224027</v>
       </c>
       <c r="E7" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F7" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.79068075404846</v>
+        <v>3.540985622532875</v>
       </c>
       <c r="D8" t="n">
-        <v>9.932187741856715</v>
+        <v>1.613980508051716</v>
       </c>
       <c r="E8" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F8" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.26935393344313</v>
+        <v>4.106270014184509</v>
       </c>
       <c r="D9" t="n">
-        <v>4.638938115971142</v>
+        <v>0.7538274438453106</v>
       </c>
       <c r="E9" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F9" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.79489714386814</v>
+        <v>2.404170785878573</v>
       </c>
       <c r="D10" t="n">
-        <v>13.09098795797737</v>
+        <v>2.127285543171322</v>
       </c>
       <c r="E10" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F10" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>11.09680421358047</v>
+        <v>1.803230684706826</v>
       </c>
       <c r="D11" t="n">
-        <v>10.86749832180919</v>
+        <v>1.765968477293994</v>
       </c>
       <c r="E11" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F11" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.4854516468064</v>
+        <v>3.816385892606041</v>
       </c>
       <c r="D12" t="n">
-        <v>20.68803812463551</v>
+        <v>3.36180619525327</v>
       </c>
       <c r="E12" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F12" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.62625032256894</v>
+        <v>8.064265677417453</v>
       </c>
       <c r="D13" t="n">
-        <v>46.72351463679228</v>
+        <v>7.592571128478746</v>
       </c>
       <c r="E13" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F13" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.5394622722381</v>
+        <v>1.712662619238692</v>
       </c>
       <c r="D14" t="n">
-        <v>37.03004177903509</v>
+        <v>6.017381789093204</v>
       </c>
       <c r="E14" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F14" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.78728817136206</v>
+        <v>5.165434327846335</v>
       </c>
       <c r="D15" t="n">
-        <v>37.3266002966078</v>
+        <v>6.065572548198768</v>
       </c>
       <c r="E15" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F15" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>81.18763460749275</v>
+        <v>13.19299062371757</v>
       </c>
       <c r="D16" t="n">
-        <v>77.95638666762062</v>
+        <v>12.66791283348835</v>
       </c>
       <c r="E16" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F16" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>58.99516259346516</v>
+        <v>9.586713921438088</v>
       </c>
       <c r="D17" t="n">
-        <v>55.23485047859602</v>
+        <v>8.975663202771853</v>
       </c>
       <c r="E17" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F17" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>27.74554368726786</v>
+        <v>4.508650849181027</v>
       </c>
       <c r="D18" t="n">
-        <v>55.6213196847654</v>
+        <v>9.038464448774377</v>
       </c>
       <c r="E18" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F18" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>37.6775880207439</v>
+        <v>6.122608053370883</v>
       </c>
       <c r="D19" t="n">
-        <v>60.16089912017158</v>
+        <v>9.776146107027882</v>
       </c>
       <c r="E19" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F19" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>86.97639308162503</v>
+        <v>14.13366387576407</v>
       </c>
       <c r="D20" t="n">
-        <v>87.13759170546123</v>
+        <v>14.15985865213745</v>
       </c>
       <c r="E20" t="n">
-        <v>21.76122061677438</v>
+        <v>3.536198350225837</v>
       </c>
       <c r="F20" t="n">
-        <v>23.53496364088603</v>
+        <v>3.824431591643981</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
